--- a/KatalonData/VLinkSmokeDataACH.xlsx
+++ b/KatalonData/VLinkSmokeDataACH.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4039" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="891">
   <si>
     <t>Result</t>
   </si>
@@ -2428,6 +2428,297 @@
   </si>
   <si>
     <t>Fri Nov 14 14:02:37 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:06 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:11 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:16 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:21 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:32 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:43 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:49 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:44:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:45:01 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:45:06 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:45:12 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:45:18 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:45:28 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:45:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:45:48 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:45:59 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:46:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:46:18 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:46:28 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:46:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:46:48 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:46:58 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:47:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:47:18 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:47:28 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:47:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:47:53 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:48:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:48:22 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:48:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:48:53 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:49:07 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:49:23 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:49:29 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:49:35 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:49:41 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:49:47 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:49:52 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:49:58 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:04 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:10 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:16 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:22 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:27 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:33 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:45 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:50:56 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:02 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:14 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:19 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:24 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:29 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:34 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:43 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:48 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:53 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:51:59 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:04 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:09 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:14 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:32 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:37 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:43 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:48 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:53 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:52:58 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:53:03 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:53:09 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:53:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:53:30 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:53:40 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:53:51 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:01 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:11 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:25 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:31 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:36 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:47 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:53 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:54:59 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:55:09 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:55:19 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:55:29 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:55:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:55:49 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 20:55:59 EST 2025</t>
   </si>
 </sst>
 </file>
@@ -2882,7 +3173,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>738</v>
+        <v>794</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -2929,7 +3220,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>739</v>
+        <v>795</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -2976,7 +3267,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>740</v>
+        <v>796</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -3023,7 +3314,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>741</v>
+        <v>797</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -3070,7 +3361,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>742</v>
+        <v>798</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -3117,7 +3408,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>743</v>
+        <v>799</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -3164,7 +3455,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>744</v>
+        <v>800</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -3291,7 +3582,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>787</v>
+        <v>884</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -3338,7 +3629,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>788</v>
+        <v>885</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -3385,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>789</v>
+        <v>886</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -3432,7 +3723,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>790</v>
+        <v>887</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -3479,7 +3770,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>791</v>
+        <v>888</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -3526,7 +3817,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>792</v>
+        <v>889</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -3573,7 +3864,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>793</v>
+        <v>890</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -3696,7 +3987,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>773</v>
+        <v>870</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -3743,7 +4034,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>774</v>
+        <v>871</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -3790,7 +4081,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>775</v>
+        <v>872</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -3837,7 +4128,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>776</v>
+        <v>873</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -3884,7 +4175,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>777</v>
+        <v>874</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -3931,7 +4222,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>778</v>
+        <v>875</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -3978,7 +4269,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>779</v>
+        <v>876</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4101,7 +4392,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>745</v>
+        <v>801</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4148,7 +4439,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>746</v>
+        <v>802</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4195,7 +4486,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>747</v>
+        <v>803</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4242,7 +4533,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>748</v>
+        <v>804</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4289,7 +4580,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>749</v>
+        <v>805</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4336,7 +4627,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4383,7 +4674,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>751</v>
+        <v>807</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4506,7 +4797,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>752</v>
+        <v>808</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4553,7 +4844,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>753</v>
+        <v>809</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4600,7 +4891,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>754</v>
+        <v>810</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4647,7 +4938,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4694,7 +4985,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>756</v>
+        <v>812</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4741,7 +5032,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>757</v>
+        <v>813</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4788,7 +5079,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>758</v>
+        <v>814</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4911,7 +5202,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>759</v>
+        <v>815</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4958,7 +5249,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>760</v>
+        <v>816</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5005,7 +5296,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>761</v>
+        <v>817</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5052,7 +5343,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>762</v>
+        <v>818</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -5099,7 +5390,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>763</v>
+        <v>819</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5146,7 +5437,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>764</v>
+        <v>820</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5193,7 +5484,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>765</v>
+        <v>821</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5316,7 +5607,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>766</v>
+        <v>822</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5363,7 +5654,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>767</v>
+        <v>823</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5410,7 +5701,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>768</v>
+        <v>824</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5457,7 +5748,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>769</v>
+        <v>825</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -5504,7 +5795,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>770</v>
+        <v>826</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5551,7 +5842,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>771</v>
+        <v>827</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5598,7 +5889,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>772</v>
+        <v>828</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5742,7 +6033,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>676</v>
+        <v>829</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5807,7 +6098,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>677</v>
+        <v>830</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5872,7 +6163,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>678</v>
+        <v>831</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5938,7 +6229,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>679</v>
+        <v>832</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -6004,7 +6295,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>680</v>
+        <v>833</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -6070,7 +6361,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>681</v>
+        <v>834</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -6136,7 +6427,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>682</v>
+        <v>835</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -6201,7 +6492,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>683</v>
+        <v>836</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -6266,7 +6557,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>684</v>
+        <v>837</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -6331,7 +6622,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>685</v>
+        <v>838</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -6396,7 +6687,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>686</v>
+        <v>839</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -6461,7 +6752,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>687</v>
+        <v>840</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -6526,7 +6817,7 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>688</v>
+        <v>841</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>17</v>
@@ -6591,7 +6882,7 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>689</v>
+        <v>842</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>17</v>
@@ -6656,7 +6947,7 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>690</v>
+        <v>843</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>17</v>
@@ -6721,7 +7012,7 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>691</v>
+        <v>844</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>17</v>
@@ -6786,7 +7077,7 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>692</v>
+        <v>845</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>17</v>
@@ -6851,7 +7142,7 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>693</v>
+        <v>846</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>17</v>
@@ -6916,7 +7207,7 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>694</v>
+        <v>847</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>17</v>
@@ -7052,7 +7343,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>695</v>
+        <v>848</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -7093,7 +7384,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>696</v>
+        <v>849</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -7134,7 +7425,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>697</v>
+        <v>850</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -7176,7 +7467,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>698</v>
+        <v>851</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -7218,7 +7509,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>699</v>
+        <v>852</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -7260,7 +7551,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>700</v>
+        <v>853</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -7302,7 +7593,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>701</v>
+        <v>854</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -7343,7 +7634,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>702</v>
+        <v>855</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -7384,7 +7675,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>703</v>
+        <v>856</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -7425,7 +7716,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>704</v>
+        <v>857</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -7543,7 +7834,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>705</v>
+        <v>858</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -7590,7 +7881,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>706</v>
+        <v>859</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -7637,7 +7928,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>707</v>
+        <v>860</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -7685,7 +7976,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>708</v>
+        <v>861</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -7733,7 +8024,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>709</v>
+        <v>862</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -7781,7 +8072,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>710</v>
+        <v>863</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -7829,7 +8120,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>711</v>
+        <v>864</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -7876,7 +8167,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>712</v>
+        <v>865</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -7923,7 +8214,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>713</v>
+        <v>866</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -7970,7 +8261,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>714</v>
+        <v>867</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -8017,7 +8308,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>715</v>
+        <v>868</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -8064,7 +8355,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>716</v>
+        <v>869</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -8188,7 +8479,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>780</v>
+        <v>877</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -8235,7 +8526,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>781</v>
+        <v>878</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -8282,7 +8573,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>782</v>
+        <v>879</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -8329,7 +8620,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>783</v>
+        <v>880</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -8376,7 +8667,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>784</v>
+        <v>881</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -8423,7 +8714,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>785</v>
+        <v>882</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -8470,7 +8761,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>786</v>
+        <v>883</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>

--- a/KatalonData/VLinkSmokeDataACH.xlsx
+++ b/KatalonData/VLinkSmokeDataACH.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4427" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4815" uniqueCount="988">
   <si>
     <t>Result</t>
   </si>
@@ -2719,6 +2719,297 @@
   </si>
   <si>
     <t>Fri Dec 12 20:55:59 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:50:55 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:51:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:52:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:52:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:52:23 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:52:33 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:52:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:52:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:53:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:53:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:53:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:53:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:53:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:53:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:54:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:54:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:54:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:54:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:55:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:55:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:55:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:55:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:33 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:56:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:57:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:58:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 17:59:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:00:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:00:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:00:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:00:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:00:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:01:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:01:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:01:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:01:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:01:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:02:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:02:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:02:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:02:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:02:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:02:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:02:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:03:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 16 18:03:17 EST 2026</t>
   </si>
 </sst>
 </file>
@@ -3173,7 +3464,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>794</v>
+        <v>891</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -3220,7 +3511,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>795</v>
+        <v>892</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -3267,7 +3558,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>796</v>
+        <v>893</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -3314,7 +3605,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>797</v>
+        <v>894</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -3361,7 +3652,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>798</v>
+        <v>895</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -3408,7 +3699,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>799</v>
+        <v>896</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -3455,7 +3746,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>800</v>
+        <v>897</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -3582,7 +3873,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>884</v>
+        <v>981</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -3629,7 +3920,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>885</v>
+        <v>982</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -3676,7 +3967,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>886</v>
+        <v>983</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -3723,7 +4014,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>887</v>
+        <v>984</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -3770,7 +4061,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>888</v>
+        <v>985</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -3817,7 +4108,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>889</v>
+        <v>986</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -3864,7 +4155,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>890</v>
+        <v>987</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -3987,7 +4278,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>870</v>
+        <v>967</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4034,7 +4325,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>871</v>
+        <v>968</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4081,7 +4372,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>872</v>
+        <v>969</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4128,7 +4419,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>873</v>
+        <v>970</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4175,7 +4466,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>874</v>
+        <v>971</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4222,7 +4513,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>875</v>
+        <v>972</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4269,7 +4560,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>876</v>
+        <v>973</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4392,7 +4683,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>801</v>
+        <v>898</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4439,7 +4730,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>802</v>
+        <v>899</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4486,7 +4777,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>803</v>
+        <v>900</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4533,7 +4824,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>804</v>
+        <v>901</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4580,7 +4871,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>805</v>
+        <v>902</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4627,7 +4918,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>806</v>
+        <v>903</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4674,7 +4965,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>807</v>
+        <v>904</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4797,7 +5088,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>808</v>
+        <v>905</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4844,7 +5135,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>809</v>
+        <v>906</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4891,7 +5182,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>810</v>
+        <v>907</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4938,7 +5229,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>811</v>
+        <v>908</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4985,7 +5276,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>812</v>
+        <v>909</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5032,7 +5323,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>813</v>
+        <v>910</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5079,7 +5370,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>814</v>
+        <v>911</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5202,7 +5493,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>815</v>
+        <v>912</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5249,7 +5540,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>816</v>
+        <v>913</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5296,7 +5587,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>817</v>
+        <v>914</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5343,7 +5634,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>818</v>
+        <v>915</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -5390,7 +5681,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>819</v>
+        <v>916</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5437,7 +5728,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>820</v>
+        <v>917</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5484,7 +5775,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>821</v>
+        <v>918</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5607,7 +5898,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>822</v>
+        <v>919</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5654,7 +5945,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>823</v>
+        <v>920</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5701,7 +5992,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>824</v>
+        <v>921</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5748,7 +6039,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>825</v>
+        <v>922</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -5795,7 +6086,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>826</v>
+        <v>923</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5842,7 +6133,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>827</v>
+        <v>924</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5889,7 +6180,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>828</v>
+        <v>925</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -6033,7 +6324,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>829</v>
+        <v>926</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -6098,7 +6389,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>830</v>
+        <v>927</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -6163,7 +6454,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>831</v>
+        <v>928</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -6229,7 +6520,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>832</v>
+        <v>929</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -6295,7 +6586,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>833</v>
+        <v>930</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -6361,7 +6652,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>834</v>
+        <v>931</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -6427,7 +6718,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>835</v>
+        <v>932</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -6492,7 +6783,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>836</v>
+        <v>933</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -6557,7 +6848,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>837</v>
+        <v>934</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -6622,7 +6913,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>838</v>
+        <v>935</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -6687,7 +6978,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>839</v>
+        <v>936</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -6752,7 +7043,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>840</v>
+        <v>937</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -6817,7 +7108,7 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>841</v>
+        <v>938</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>17</v>
@@ -6882,7 +7173,7 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>842</v>
+        <v>939</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>17</v>
@@ -6947,7 +7238,7 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>843</v>
+        <v>940</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>17</v>
@@ -7012,7 +7303,7 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>844</v>
+        <v>941</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>17</v>
@@ -7077,7 +7368,7 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>845</v>
+        <v>942</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>17</v>
@@ -7142,7 +7433,7 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>846</v>
+        <v>943</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>17</v>
@@ -7207,7 +7498,7 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>847</v>
+        <v>944</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>17</v>
@@ -7343,7 +7634,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>848</v>
+        <v>945</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -7384,7 +7675,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>849</v>
+        <v>946</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -7425,7 +7716,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>850</v>
+        <v>947</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -7467,7 +7758,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>851</v>
+        <v>948</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -7509,7 +7800,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>852</v>
+        <v>949</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -7551,7 +7842,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>853</v>
+        <v>950</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -7593,7 +7884,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>854</v>
+        <v>951</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -7634,7 +7925,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>855</v>
+        <v>952</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -7675,7 +7966,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>856</v>
+        <v>953</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -7716,7 +8007,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>857</v>
+        <v>954</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -7834,7 +8125,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>858</v>
+        <v>955</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -7881,7 +8172,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>859</v>
+        <v>956</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -7928,7 +8219,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>860</v>
+        <v>957</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -7976,7 +8267,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>861</v>
+        <v>958</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -8024,7 +8315,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>862</v>
+        <v>959</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -8072,7 +8363,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>863</v>
+        <v>960</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -8120,7 +8411,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>864</v>
+        <v>961</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -8167,7 +8458,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>865</v>
+        <v>962</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -8214,7 +8505,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>866</v>
+        <v>963</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -8261,7 +8552,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>867</v>
+        <v>964</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -8308,7 +8599,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>868</v>
+        <v>965</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -8355,7 +8646,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>869</v>
+        <v>966</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -8479,7 +8770,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>877</v>
+        <v>974</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -8523,10 +8814,10 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>878</v>
+        <v>975</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -8573,7 +8864,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>879</v>
+        <v>976</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -8620,7 +8911,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>880</v>
+        <v>977</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -8667,7 +8958,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>881</v>
+        <v>978</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -8714,7 +9005,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>882</v>
+        <v>979</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -8761,7 +9052,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>883</v>
+        <v>980</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>

--- a/KatalonData/VLinkSmokeDataACH.xlsx
+++ b/KatalonData/VLinkSmokeDataACH.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4815" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5427" uniqueCount="1141">
   <si>
     <t>Result</t>
   </si>
@@ -3010,6 +3010,465 @@
   </si>
   <si>
     <t>Fri Jan 16 18:03:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:20:55 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:22 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:21:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:22:09 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:22:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:22:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:22:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:22:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:23:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:23:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:23:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:23:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:23:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:23:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:24:09 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:24:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:24:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:24:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:25:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:25:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:25:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:25:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:26:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:26:22 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:26:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:26:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:26:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:26:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:26:55 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:22 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:27:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:28:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:33 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:29:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:30:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:30:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:30:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:30:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:30:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:30:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:30:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:30:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:31:09 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:31:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:31:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:31:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:31:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:31:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:31:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:32:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:32:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:32:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:32:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:32:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:32:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:32:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:33:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:33:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 21:33:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:08:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:09:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:09:09 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:09:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:09:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:09:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:09:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:09:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:09:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:10:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:10:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:10:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:10:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:10:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:11:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:11:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:11:22 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:11:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:11:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:11:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:12:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:12:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:12:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:12:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:13:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:13:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:13:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:14:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:14:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:14:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:14:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:14:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:14:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:15:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:16:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:16:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:16:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:16:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:16:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 13:17:03 EST 2026</t>
   </si>
 </sst>
 </file>
@@ -3464,7 +3923,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>891</v>
+        <v>1085</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -3511,7 +3970,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>892</v>
+        <v>1086</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -3558,7 +4017,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>893</v>
+        <v>1087</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -3605,7 +4064,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>894</v>
+        <v>1088</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -3652,7 +4111,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>895</v>
+        <v>1089</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -3699,7 +4158,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>896</v>
+        <v>1090</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -3746,7 +4205,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>897</v>
+        <v>1091</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -3873,7 +4332,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>981</v>
+        <v>1134</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -3920,7 +4379,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>982</v>
+        <v>1135</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -3967,7 +4426,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>983</v>
+        <v>1136</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4014,7 +4473,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>984</v>
+        <v>1137</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4061,7 +4520,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>985</v>
+        <v>1138</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4108,7 +4567,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>986</v>
+        <v>1139</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4155,7 +4614,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>987</v>
+        <v>1140</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4278,7 +4737,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>967</v>
+        <v>1120</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4325,7 +4784,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>968</v>
+        <v>1121</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4372,7 +4831,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>969</v>
+        <v>1122</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4419,7 +4878,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>970</v>
+        <v>1123</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4466,7 +4925,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>971</v>
+        <v>1124</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4513,7 +4972,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>972</v>
+        <v>1125</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4560,7 +5019,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>973</v>
+        <v>1126</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4683,7 +5142,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>898</v>
+        <v>1092</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4730,7 +5189,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>899</v>
+        <v>1093</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4777,7 +5236,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>900</v>
+        <v>1094</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4824,7 +5283,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>901</v>
+        <v>1095</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4871,7 +5330,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>902</v>
+        <v>1096</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4918,7 +5377,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>903</v>
+        <v>1097</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4965,7 +5424,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>904</v>
+        <v>1098</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5088,7 +5547,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>905</v>
+        <v>1099</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5135,7 +5594,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>906</v>
+        <v>1100</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5182,7 +5641,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>907</v>
+        <v>1101</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5229,7 +5688,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>908</v>
+        <v>1102</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -5276,7 +5735,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>909</v>
+        <v>1103</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5323,7 +5782,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>910</v>
+        <v>1104</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5370,7 +5829,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>911</v>
+        <v>1105</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5493,7 +5952,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>912</v>
+        <v>1106</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5540,7 +5999,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>913</v>
+        <v>1107</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5587,7 +6046,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>914</v>
+        <v>1108</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5634,7 +6093,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>915</v>
+        <v>1109</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -5681,7 +6140,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>916</v>
+        <v>1110</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5728,7 +6187,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>917</v>
+        <v>1111</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5775,7 +6234,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>918</v>
+        <v>1112</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5898,7 +6357,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>919</v>
+        <v>1113</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5945,7 +6404,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>920</v>
+        <v>1114</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5992,7 +6451,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>921</v>
+        <v>1115</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -6039,7 +6498,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>922</v>
+        <v>1116</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -6086,7 +6545,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>923</v>
+        <v>1117</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -6133,7 +6592,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>924</v>
+        <v>1118</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -6180,7 +6639,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>925</v>
+        <v>1119</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -6324,7 +6783,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>926</v>
+        <v>1023</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -6389,7 +6848,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>927</v>
+        <v>1024</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -6454,7 +6913,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>928</v>
+        <v>1025</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -6520,7 +6979,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>929</v>
+        <v>1026</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -6586,7 +7045,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>930</v>
+        <v>1027</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -6652,7 +7111,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>931</v>
+        <v>1028</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -6718,7 +7177,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>932</v>
+        <v>1029</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -6783,7 +7242,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>933</v>
+        <v>1030</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -6848,7 +7307,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>934</v>
+        <v>1031</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -6913,7 +7372,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>935</v>
+        <v>1032</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -6978,7 +7437,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>936</v>
+        <v>1033</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -7043,7 +7502,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>937</v>
+        <v>1034</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -7108,7 +7567,7 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>938</v>
+        <v>1035</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>17</v>
@@ -7173,7 +7632,7 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>939</v>
+        <v>1036</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>17</v>
@@ -7238,7 +7697,7 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>940</v>
+        <v>1037</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>17</v>
@@ -7303,7 +7762,7 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>941</v>
+        <v>1038</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>17</v>
@@ -7368,7 +7827,7 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>942</v>
+        <v>1039</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>17</v>
@@ -7433,7 +7892,7 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>943</v>
+        <v>1040</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>17</v>
@@ -7498,7 +7957,7 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>944</v>
+        <v>1041</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>17</v>
@@ -7634,7 +8093,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>945</v>
+        <v>1042</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -7675,7 +8134,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>946</v>
+        <v>1043</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -7716,7 +8175,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>947</v>
+        <v>1044</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -7758,7 +8217,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>948</v>
+        <v>1045</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -7800,7 +8259,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>949</v>
+        <v>1046</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -7842,7 +8301,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>950</v>
+        <v>1047</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -7884,7 +8343,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>951</v>
+        <v>1048</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -7925,7 +8384,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>952</v>
+        <v>1049</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -7966,7 +8425,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>953</v>
+        <v>1050</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -8007,7 +8466,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>954</v>
+        <v>1051</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -8125,7 +8584,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>955</v>
+        <v>1052</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -8172,7 +8631,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>956</v>
+        <v>1053</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -8219,7 +8678,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>957</v>
+        <v>1054</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -8267,7 +8726,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>958</v>
+        <v>1055</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -8315,7 +8774,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>959</v>
+        <v>1056</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -8363,7 +8822,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>960</v>
+        <v>1057</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -8411,7 +8870,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>961</v>
+        <v>1058</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -8458,7 +8917,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>962</v>
+        <v>1059</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -8505,7 +8964,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>963</v>
+        <v>1060</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -8552,7 +9011,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>964</v>
+        <v>1061</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -8599,7 +9058,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>965</v>
+        <v>1062</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -8646,7 +9105,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>966</v>
+        <v>1063</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -8770,7 +9229,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>974</v>
+        <v>1127</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -8814,10 +9273,10 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>975</v>
+        <v>1128</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -8864,7 +9323,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>976</v>
+        <v>1129</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -8911,7 +9370,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>977</v>
+        <v>1130</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -8958,7 +9417,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>978</v>
+        <v>1131</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -9005,7 +9464,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>979</v>
+        <v>1132</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -9052,7 +9511,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>980</v>
+        <v>1133</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>

--- a/KatalonData/VLinkSmokeDataACH.xlsx
+++ b/KatalonData/VLinkSmokeDataACH.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5427" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5621" uniqueCount="1238">
   <si>
     <t>Result</t>
   </si>
@@ -3469,6 +3469,297 @@
   </si>
   <si>
     <t>Sat Feb 14 13:17:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:03:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:03:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:04:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:04:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:04:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:04:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:04:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:04:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:04:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:04:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:05:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:05:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:05:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:05:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:05:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:05:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:05:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:06:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:06:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:06:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:06:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:07:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:07:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:07:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:07:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:07:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:08:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:08:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:08:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:09:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:09:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:09:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:10:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:10:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:10:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:11:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:11:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:11:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:11:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:11:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:11:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:11:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:12:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:12:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:12:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:12:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:12:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:12:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:12:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:13:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:13:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:13:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:13:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:13:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:13:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:13:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:13:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:14:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:15:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:15:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:15:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:15:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:15:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:15:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:15:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:15:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:16:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:16:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:16:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:16:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:16:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:16:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:17:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:17:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:17:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:17:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:18:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:18:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:18:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:18:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:18:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:18:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:18:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:19:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:19:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:19:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:19:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:19:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 14:20:12 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -3923,7 +4214,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1085</v>
+        <v>1141</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -3970,7 +4261,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1086</v>
+        <v>1142</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4017,7 +4308,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1087</v>
+        <v>1143</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4064,7 +4355,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1088</v>
+        <v>1144</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4111,7 +4402,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1089</v>
+        <v>1145</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4158,7 +4449,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1090</v>
+        <v>1146</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4205,7 +4496,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1091</v>
+        <v>1147</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4332,7 +4623,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1134</v>
+        <v>1231</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4379,7 +4670,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1135</v>
+        <v>1232</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4426,7 +4717,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1136</v>
+        <v>1233</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4473,7 +4764,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1137</v>
+        <v>1234</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4520,7 +4811,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1138</v>
+        <v>1235</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4567,7 +4858,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1139</v>
+        <v>1236</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -4614,7 +4905,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1140</v>
+        <v>1237</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -4737,7 +5028,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1120</v>
+        <v>1217</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -4784,7 +5075,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1121</v>
+        <v>1218</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -4831,7 +5122,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1122</v>
+        <v>1219</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -4878,7 +5169,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1123</v>
+        <v>1220</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -4925,7 +5216,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1124</v>
+        <v>1221</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -4972,7 +5263,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1125</v>
+        <v>1222</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5019,7 +5310,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1126</v>
+        <v>1223</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5142,7 +5433,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1092</v>
+        <v>1148</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5189,7 +5480,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1093</v>
+        <v>1149</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5236,7 +5527,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1094</v>
+        <v>1150</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5283,7 +5574,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1095</v>
+        <v>1151</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -5330,7 +5621,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1096</v>
+        <v>1152</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5377,7 +5668,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1097</v>
+        <v>1153</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5424,7 +5715,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1098</v>
+        <v>1154</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5547,7 +5838,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1099</v>
+        <v>1155</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5594,7 +5885,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1100</v>
+        <v>1156</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -5641,7 +5932,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1101</v>
+        <v>1157</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -5688,7 +5979,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1102</v>
+        <v>1158</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -5735,7 +6026,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1103</v>
+        <v>1159</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -5782,7 +6073,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1104</v>
+        <v>1160</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -5829,7 +6120,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1105</v>
+        <v>1161</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -5952,7 +6243,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1106</v>
+        <v>1162</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -5999,7 +6290,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1107</v>
+        <v>1163</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -6046,7 +6337,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1108</v>
+        <v>1164</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -6093,7 +6384,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1109</v>
+        <v>1165</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -6140,7 +6431,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1110</v>
+        <v>1166</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -6187,7 +6478,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1111</v>
+        <v>1167</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -6234,7 +6525,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1112</v>
+        <v>1168</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -6357,7 +6648,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1113</v>
+        <v>1169</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -6404,7 +6695,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1114</v>
+        <v>1170</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -6451,7 +6742,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1115</v>
+        <v>1171</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -6498,7 +6789,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1116</v>
+        <v>1172</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -6545,7 +6836,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1117</v>
+        <v>1173</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -6592,7 +6883,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1118</v>
+        <v>1174</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -6639,7 +6930,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1119</v>
+        <v>1175</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -6783,7 +7074,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1023</v>
+        <v>1176</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -6848,7 +7139,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1024</v>
+        <v>1177</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -6913,7 +7204,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1025</v>
+        <v>1178</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -6979,7 +7270,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1026</v>
+        <v>1179</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -7045,7 +7336,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1027</v>
+        <v>1180</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -7111,7 +7402,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1028</v>
+        <v>1181</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -7177,7 +7468,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1029</v>
+        <v>1182</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -7242,7 +7533,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>1030</v>
+        <v>1183</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -7307,7 +7598,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>1031</v>
+        <v>1184</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -7372,7 +7663,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>1032</v>
+        <v>1185</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -7437,7 +7728,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>1033</v>
+        <v>1186</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -7502,7 +7793,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>1034</v>
+        <v>1187</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -7567,7 +7858,7 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>1035</v>
+        <v>1188</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>17</v>
@@ -7632,7 +7923,7 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>1036</v>
+        <v>1189</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>17</v>
@@ -7697,7 +7988,7 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>1037</v>
+        <v>1190</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>17</v>
@@ -7762,7 +8053,7 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>1038</v>
+        <v>1191</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>17</v>
@@ -7827,7 +8118,7 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>1039</v>
+        <v>1192</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>17</v>
@@ -7892,7 +8183,7 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>1040</v>
+        <v>1193</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>17</v>
@@ -7957,7 +8248,7 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>1041</v>
+        <v>1194</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>17</v>
@@ -8093,7 +8384,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1042</v>
+        <v>1195</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -8134,7 +8425,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1043</v>
+        <v>1196</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -8175,7 +8466,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1044</v>
+        <v>1197</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -8217,7 +8508,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1045</v>
+        <v>1198</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -8259,7 +8550,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1046</v>
+        <v>1199</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -8301,7 +8592,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1047</v>
+        <v>1200</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -8343,7 +8634,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1048</v>
+        <v>1201</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -8384,7 +8675,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -8425,7 +8716,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>1050</v>
+        <v>1203</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -8466,7 +8757,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>1051</v>
+        <v>1204</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -8584,7 +8875,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1052</v>
+        <v>1205</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -8631,7 +8922,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1053</v>
+        <v>1206</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -8678,7 +8969,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1054</v>
+        <v>1207</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -8726,7 +9017,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1055</v>
+        <v>1208</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -8774,7 +9065,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1056</v>
+        <v>1209</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -8822,7 +9113,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1057</v>
+        <v>1210</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -8870,7 +9161,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1058</v>
+        <v>1211</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -8917,7 +9208,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>1059</v>
+        <v>1212</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -8964,7 +9255,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>1060</v>
+        <v>1213</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -9011,7 +9302,7 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>1061</v>
+        <v>1214</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -9058,7 +9349,7 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>1062</v>
+        <v>1215</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -9105,7 +9396,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>1063</v>
+        <v>1216</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -9229,7 +9520,7 @@
         <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>1127</v>
+        <v>1224</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
@@ -9276,7 +9567,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>1128</v>
+        <v>1225</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
@@ -9323,7 +9614,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>1129</v>
+        <v>1226</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -9370,7 +9661,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>1130</v>
+        <v>1227</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -9417,7 +9708,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>1131</v>
+        <v>1228</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
@@ -9464,7 +9755,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>1132</v>
+        <v>1229</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
@@ -9511,7 +9802,7 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>1133</v>
+        <v>1230</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
